--- a/Visuals for Query Resuls .xlsx
+++ b/Visuals for Query Resuls .xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
-  <workbookPr defaultThemeVersion="166925"/>
+  <workbookPr hidePivotFieldList="1" defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/a325add542d55a26/Desktop/Data Analyst Bootcamp/Data Analyst Bootcamp/Job Application Tips/2. SQL Project for your Portfolio/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="485" documentId="8_{5B3FAE9F-4211-43F5-A11C-B0C5D8BA253E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3EA1B642-49AA-4006-B761-99E2690ABAB2}"/>
+  <xr:revisionPtr revIDLastSave="490" documentId="8_{5B3FAE9F-4211-43F5-A11C-B0C5D8BA253E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA3DE5F0-7CF1-48E7-9021-A85B87429177}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" activeTab="6" xr2:uid="{86640312-D82A-4A45-9EB1-843FF8E202E0}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="112" uniqueCount="97">
   <si>
     <t>segment</t>
   </si>
@@ -958,6 +958,9 @@
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="42" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -981,9 +984,6 @@
     </xf>
     <xf numFmtId="0" fontId="18" fillId="33" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="43">
@@ -1031,126 +1031,7 @@
     <cellStyle name="Total" xfId="17" builtinId="25" customBuiltin="1"/>
     <cellStyle name="Warning Text" xfId="14" builtinId="11" customBuiltin="1"/>
   </cellStyles>
-  <dxfs count="39">
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.00,,&quot;M&quot;"/>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <sz val="12"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
-    </dxf>
-    <dxf>
-      <numFmt numFmtId="164" formatCode="0.00,,&quot;M&quot;"/>
-    </dxf>
+  <dxfs count="27">
     <dxf>
       <numFmt numFmtId="14" formatCode="0.00%"/>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1163,6 +1044,9 @@
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <alignment horizontal="left" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
@@ -1265,6 +1149,64 @@
     </dxf>
     <dxf>
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <sz val="12"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+      </font>
+    </dxf>
+    <dxf>
+      <numFmt numFmtId="164" formatCode="0.00,,&quot;M&quot;"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -2700,7 +2642,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[SQL Results Visuals.xlsx]7!PivotTable6</c:name>
+    <c:name>[Visuals for Query Resuls .xlsx]7!PivotTable6</c:name>
     <c:fmtId val="11"/>
   </c:pivotSource>
   <c:chart>
@@ -2859,9 +2801,9 @@
         <c:spPr>
           <a:ln w="38100" cap="rnd">
             <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="40000"/>
-                <a:lumOff val="60000"/>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="60000"/>
+                <a:lumOff val="40000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:round/>
@@ -2873,15 +2815,15 @@
           <c:size val="8"/>
           <c:spPr>
             <a:solidFill>
-              <a:schemeClr val="accent2">
-                <a:lumMod val="75000"/>
+              <a:schemeClr val="accent6">
+                <a:lumMod val="50000"/>
               </a:schemeClr>
             </a:solidFill>
             <a:ln>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
                 </a:schemeClr>
               </a:solidFill>
             </a:ln>
@@ -2964,9 +2906,9 @@
           <c:spPr>
             <a:ln w="38100" cap="rnd">
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="40000"/>
-                  <a:lumOff val="60000"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="60000"/>
+                  <a:lumOff val="40000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:round/>
@@ -2978,15 +2920,15 @@
             <c:size val="8"/>
             <c:spPr>
               <a:solidFill>
-                <a:schemeClr val="accent2">
-                  <a:lumMod val="75000"/>
+                <a:schemeClr val="accent6">
+                  <a:lumMod val="50000"/>
                 </a:schemeClr>
               </a:solidFill>
               <a:ln>
                 <a:solidFill>
-                  <a:schemeClr val="accent2">
-                    <a:lumMod val="40000"/>
-                    <a:lumOff val="60000"/>
+                  <a:schemeClr val="accent6">
+                    <a:lumMod val="60000"/>
+                    <a:lumOff val="40000"/>
                   </a:schemeClr>
                 </a:solidFill>
               </a:ln>
@@ -3052,9 +2994,9 @@
           </c:dLbls>
           <c:cat>
             <c:multiLvlStrRef>
-              <c:f>'7'!$A$6:$B$57</c:f>
+              <c:f>'7'!$A$6:$B$21</c:f>
               <c:multiLvlStrCache>
-                <c:ptCount val="52"/>
+                <c:ptCount val="16"/>
                 <c:lvl>
                   <c:pt idx="0">
                     <c:v>September</c:v>
@@ -3104,129 +3046,12 @@
                   <c:pt idx="15">
                     <c:v>December</c:v>
                   </c:pt>
-                  <c:pt idx="16">
-                    <c:v>January</c:v>
-                  </c:pt>
-                  <c:pt idx="17">
-                    <c:v>February</c:v>
-                  </c:pt>
-                  <c:pt idx="18">
-                    <c:v>March</c:v>
-                  </c:pt>
-                  <c:pt idx="19">
-                    <c:v>April</c:v>
-                  </c:pt>
-                  <c:pt idx="20">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="21">
-                    <c:v>June</c:v>
-                  </c:pt>
-                  <c:pt idx="22">
-                    <c:v>July</c:v>
-                  </c:pt>
-                  <c:pt idx="23">
-                    <c:v>August</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>September</c:v>
-                  </c:pt>
-                  <c:pt idx="25">
-                    <c:v>October</c:v>
-                  </c:pt>
-                  <c:pt idx="26">
-                    <c:v>November</c:v>
-                  </c:pt>
-                  <c:pt idx="27">
-                    <c:v>December</c:v>
-                  </c:pt>
-                  <c:pt idx="28">
-                    <c:v>January</c:v>
-                  </c:pt>
-                  <c:pt idx="29">
-                    <c:v>February</c:v>
-                  </c:pt>
-                  <c:pt idx="30">
-                    <c:v>March</c:v>
-                  </c:pt>
-                  <c:pt idx="31">
-                    <c:v>April</c:v>
-                  </c:pt>
-                  <c:pt idx="32">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="33">
-                    <c:v>June</c:v>
-                  </c:pt>
-                  <c:pt idx="34">
-                    <c:v>July</c:v>
-                  </c:pt>
-                  <c:pt idx="35">
-                    <c:v>August</c:v>
-                  </c:pt>
-                  <c:pt idx="36">
-                    <c:v>September</c:v>
-                  </c:pt>
-                  <c:pt idx="37">
-                    <c:v>October</c:v>
-                  </c:pt>
-                  <c:pt idx="38">
-                    <c:v>November</c:v>
-                  </c:pt>
-                  <c:pt idx="39">
-                    <c:v>December</c:v>
-                  </c:pt>
-                  <c:pt idx="40">
-                    <c:v>January</c:v>
-                  </c:pt>
-                  <c:pt idx="41">
-                    <c:v>February</c:v>
-                  </c:pt>
-                  <c:pt idx="42">
-                    <c:v>March</c:v>
-                  </c:pt>
-                  <c:pt idx="43">
-                    <c:v>April</c:v>
-                  </c:pt>
-                  <c:pt idx="44">
-                    <c:v>May</c:v>
-                  </c:pt>
-                  <c:pt idx="45">
-                    <c:v>June</c:v>
-                  </c:pt>
-                  <c:pt idx="46">
-                    <c:v>July</c:v>
-                  </c:pt>
-                  <c:pt idx="47">
-                    <c:v>August</c:v>
-                  </c:pt>
-                  <c:pt idx="48">
-                    <c:v>September</c:v>
-                  </c:pt>
-                  <c:pt idx="49">
-                    <c:v>October</c:v>
-                  </c:pt>
-                  <c:pt idx="50">
-                    <c:v>November</c:v>
-                  </c:pt>
-                  <c:pt idx="51">
-                    <c:v>December</c:v>
-                  </c:pt>
                 </c:lvl>
                 <c:lvl>
                   <c:pt idx="0">
-                    <c:v>2018</c:v>
+                    <c:v>2021</c:v>
                   </c:pt>
                   <c:pt idx="12">
-                    <c:v>2019</c:v>
-                  </c:pt>
-                  <c:pt idx="24">
-                    <c:v>2020</c:v>
-                  </c:pt>
-                  <c:pt idx="36">
-                    <c:v>2021</c:v>
-                  </c:pt>
-                  <c:pt idx="48">
                     <c:v>2022</c:v>
                   </c:pt>
                 </c:lvl>
@@ -3235,164 +3060,56 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>'7'!$C$6:$C$57</c:f>
+              <c:f>'7'!$C$6:$C$21</c:f>
               <c:numCache>
                 <c:formatCode>0.00,,"M"</c:formatCode>
-                <c:ptCount val="52"/>
+                <c:ptCount val="16"/>
                 <c:pt idx="0">
-                  <c:v>2347703.88</c:v>
+                  <c:v>37752848.189999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>2462780.5499999998</c:v>
+                  <c:v>40444450.560000002</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3766114.43</c:v>
+                  <c:v>62302295.57</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2390015.56</c:v>
+                  <c:v>39306619.909999996</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2285937.67</c:v>
+                  <c:v>37704996.299999997</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1985466.36</c:v>
+                  <c:v>30852326.32</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>2219880.14</c:v>
+                  <c:v>36972600.020000003</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>1392024.51</c:v>
+                  <c:v>22147394.989999998</c:v>
                 </c:pt>
                 <c:pt idx="8">
-                  <c:v>2310946.52</c:v>
+                  <c:v>37037201.240000002</c:v>
                 </c:pt>
                 <c:pt idx="9">
-                  <c:v>1976109.61</c:v>
+                  <c:v>29887193.879999999</c:v>
                 </c:pt>
                 <c:pt idx="10">
-                  <c:v>2224693.7599999998</c:v>
+                  <c:v>36677913.909999996</c:v>
                 </c:pt>
                 <c:pt idx="11">
-                  <c:v>1498728.56</c:v>
+                  <c:v>21839400.719999999</c:v>
                 </c:pt>
                 <c:pt idx="12">
-                  <c:v>7860039.25</c:v>
+                  <c:v>153599487.94999999</c:v>
                 </c:pt>
                 <c:pt idx="13">
-                  <c:v>8496754.2300000004</c:v>
+                  <c:v>159240254.33000001</c:v>
                 </c:pt>
                 <c:pt idx="14">
-                  <c:v>12362495.369999999</c:v>
+                  <c:v>259105977.18000001</c:v>
                 </c:pt>
                 <c:pt idx="15">
-                  <c:v>8364101.0199999996</c:v>
-                </c:pt>
-                <c:pt idx="16">
-                  <c:v>7607522.3600000003</c:v>
-                </c:pt>
-                <c:pt idx="17">
-                  <c:v>6218859.5700000003</c:v>
-                </c:pt>
-                <c:pt idx="18">
-                  <c:v>7307169.1500000004</c:v>
-                </c:pt>
-                <c:pt idx="19">
-                  <c:v>4677628.0999999996</c:v>
-                </c:pt>
-                <c:pt idx="20">
-                  <c:v>7796837.2999999998</c:v>
-                </c:pt>
-                <c:pt idx="21">
-                  <c:v>6580393.9800000004</c:v>
-                </c:pt>
-                <c:pt idx="22">
-                  <c:v>7296958.9800000004</c:v>
-                </c:pt>
-                <c:pt idx="23">
-                  <c:v>4630439.42</c:v>
-                </c:pt>
-                <c:pt idx="24">
-                  <c:v>17040562.239999998</c:v>
-                </c:pt>
-                <c:pt idx="25">
-                  <c:v>19475069.34</c:v>
-                </c:pt>
-                <c:pt idx="26">
-                  <c:v>28512004.149999999</c:v>
-                </c:pt>
-                <c:pt idx="27">
-                  <c:v>18322529.100000001</c:v>
-                </c:pt>
-                <c:pt idx="28">
-                  <c:v>18009123.489999998</c:v>
-                </c:pt>
-                <c:pt idx="29">
-                  <c:v>15171931.84</c:v>
-                </c:pt>
-                <c:pt idx="30">
-                  <c:v>1422525.16</c:v>
-                </c:pt>
-                <c:pt idx="31">
-                  <c:v>1492369.18</c:v>
-                </c:pt>
-                <c:pt idx="32">
-                  <c:v>2971173.85</c:v>
-                </c:pt>
-                <c:pt idx="33">
-                  <c:v>6451963.4100000001</c:v>
-                </c:pt>
-                <c:pt idx="34">
-                  <c:v>9685828.6300000008</c:v>
-                </c:pt>
-                <c:pt idx="35">
-                  <c:v>10599401.49</c:v>
-                </c:pt>
-                <c:pt idx="36">
-                  <c:v>37752848.189999998</c:v>
-                </c:pt>
-                <c:pt idx="37">
-                  <c:v>40444450.560000002</c:v>
-                </c:pt>
-                <c:pt idx="38">
-                  <c:v>62302295.57</c:v>
-                </c:pt>
-                <c:pt idx="39">
-                  <c:v>39306619.909999996</c:v>
-                </c:pt>
-                <c:pt idx="40">
-                  <c:v>37704996.299999997</c:v>
-                </c:pt>
-                <c:pt idx="41">
-                  <c:v>30852326.32</c:v>
-                </c:pt>
-                <c:pt idx="42">
-                  <c:v>36972600.020000003</c:v>
-                </c:pt>
-                <c:pt idx="43">
-                  <c:v>22147394.989999998</c:v>
-                </c:pt>
-                <c:pt idx="44">
-                  <c:v>37037201.240000002</c:v>
-                </c:pt>
-                <c:pt idx="45">
-                  <c:v>29887193.879999999</c:v>
-                </c:pt>
-                <c:pt idx="46">
-                  <c:v>36677913.909999996</c:v>
-                </c:pt>
-                <c:pt idx="47">
-                  <c:v>21839400.719999999</c:v>
-                </c:pt>
-                <c:pt idx="48">
-                  <c:v>153599487.94999999</c:v>
-                </c:pt>
-                <c:pt idx="49">
-                  <c:v>159240254.33000001</c:v>
-                </c:pt>
-                <c:pt idx="50">
-                  <c:v>259105977.18000001</c:v>
-                </c:pt>
-                <c:pt idx="51">
                   <c:v>161727839.58000001</c:v>
                 </c:pt>
               </c:numCache>
@@ -4349,7 +4066,7 @@
     </mc:Fallback>
   </mc:AlternateContent>
   <c:pivotSource>
-    <c:name>[SQL Results Visuals.xlsx]10!PivotTable18</c:name>
+    <c:name>[Visuals for Query Resuls .xlsx]10!PivotTable18</c:name>
     <c:fmtId val="4"/>
   </c:pivotSource>
   <c:chart>
@@ -9587,8 +9304,8 @@
 </file>
 
 <file path=xl/pivotTables/pivotTable1.xml><?xml version="1.0" encoding="utf-8"?>
-<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A8A33D5-F649-4099-B893-C1C748A289C6}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="44">
-  <location ref="A5:C57" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
+<pivotTableDefinition xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr" xr:uid="{6A8A33D5-F649-4099-B893-C1C748A289C6}" name="PivotTable6" cacheId="1" applyNumberFormats="0" applyBorderFormats="0" applyFontFormats="0" applyPatternFormats="0" applyAlignmentFormats="0" applyWidthHeightFormats="1" dataCaption="Values" updatedVersion="8" minRefreshableVersion="3" useAutoFormatting="1" rowGrandTotals="0" colGrandTotals="0" itemPrintTitles="1" createdVersion="8" indent="0" compact="0" compactData="0" multipleFieldFilters="0" chartFormat="55">
+  <location ref="A5:C21" firstHeaderRow="1" firstDataRow="1" firstDataCol="2"/>
   <pivotFields count="3">
     <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" showAll="0" defaultSubtotal="0">
       <items count="12">
@@ -9608,9 +9325,9 @@
     </pivotField>
     <pivotField axis="axisRow" compact="0" outline="0" subtotalTop="0" multipleItemSelectionAllowed="1" showAll="0" defaultSubtotal="0">
       <items count="5">
-        <item x="0"/>
-        <item x="1"/>
-        <item x="2"/>
+        <item h="1" x="0"/>
+        <item h="1" x="1"/>
+        <item h="1" x="2"/>
         <item x="3"/>
         <item x="4"/>
       </items>
@@ -9621,118 +9338,7 @@
     <field x="1"/>
     <field x="0"/>
   </rowFields>
-  <rowItems count="52">
-    <i>
-      <x/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="1"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
-    <i>
-      <x v="2"/>
-      <x/>
-    </i>
-    <i r="1">
-      <x v="1"/>
-    </i>
-    <i r="1">
-      <x v="2"/>
-    </i>
-    <i r="1">
-      <x v="3"/>
-    </i>
-    <i r="1">
-      <x v="4"/>
-    </i>
-    <i r="1">
-      <x v="5"/>
-    </i>
-    <i r="1">
-      <x v="6"/>
-    </i>
-    <i r="1">
-      <x v="7"/>
-    </i>
-    <i r="1">
-      <x v="8"/>
-    </i>
-    <i r="1">
-      <x v="9"/>
-    </i>
-    <i r="1">
-      <x v="10"/>
-    </i>
-    <i r="1">
-      <x v="11"/>
-    </i>
+  <rowItems count="16">
     <i>
       <x v="3"/>
       <x/>
@@ -9791,13 +9397,13 @@
     <dataField name="Sum of gross_sales_amount" fld="2" baseField="0" baseItem="0" numFmtId="164"/>
   </dataFields>
   <formats count="12">
-    <format dxfId="24">
+    <format dxfId="26">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="23">
+    <format dxfId="25">
       <pivotArea outline="0" collapsedLevelsAreSubtotals="1" fieldPosition="0"/>
     </format>
-    <format dxfId="22">
+    <format dxfId="24">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9807,7 +9413,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="21">
+    <format dxfId="23">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9817,7 +9423,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="20">
+    <format dxfId="22">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9827,7 +9433,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="19">
+    <format dxfId="21">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9837,7 +9443,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="18">
+    <format dxfId="20">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="4">
@@ -9852,7 +9458,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="17">
+    <format dxfId="19">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9862,7 +9468,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="16">
+    <format dxfId="18">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9872,7 +9478,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="15">
+    <format dxfId="17">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9882,7 +9488,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="14">
+    <format dxfId="16">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="0"/>
@@ -9892,7 +9498,7 @@
         </references>
       </pivotArea>
     </format>
-    <format dxfId="13">
+    <format dxfId="15">
       <pivotArea dataOnly="0" labelOnly="1" outline="0" fieldPosition="0">
         <references count="2">
           <reference field="0" count="4">
@@ -9908,7 +9514,7 @@
       </pivotArea>
     </format>
   </formats>
-  <chartFormats count="4">
+  <chartFormats count="6">
     <chartFormat chart="6" format="0" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
@@ -9937,6 +9543,24 @@
       </pivotArea>
     </chartFormat>
     <chartFormat chart="11" format="2" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="53" format="3" series="1">
+      <pivotArea type="data" outline="0" fieldPosition="0">
+        <references count="1">
+          <reference field="4294967294" count="1" selected="0">
+            <x v="0"/>
+          </reference>
+        </references>
+      </pivotArea>
+    </chartFormat>
+    <chartFormat chart="54" format="4" series="1">
       <pivotArea type="data" outline="0" fieldPosition="0">
         <references count="1">
           <reference field="4294967294" count="1" selected="0">
@@ -10092,20 +9716,20 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4433C211-868D-4E23-BF8F-2C9327C3157D}" name="Table5" displayName="Table5" ref="B5:B13" totalsRowShown="0" dataDxfId="38">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{4433C211-868D-4E23-BF8F-2C9327C3157D}" name="Table5" displayName="Table5" ref="B5:B13" totalsRowShown="0" dataDxfId="14">
   <tableColumns count="1">
-    <tableColumn id="1" xr3:uid="{C4FDC313-B282-4390-A504-9B349ACD3062}" name="Market" dataDxfId="37"/>
+    <tableColumn id="1" xr3:uid="{C4FDC313-B282-4390-A504-9B349ACD3062}" name="Market" dataDxfId="13"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2E25067-0CA2-41AB-8EB6-AFA23CC687F7}" name="Table1" displayName="Table1" ref="B6:D7" totalsRowShown="0" headerRowDxfId="36" headerRowBorderDxfId="35" tableBorderDxfId="34" totalsRowBorderDxfId="33">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{B2E25067-0CA2-41AB-8EB6-AFA23CC687F7}" name="Table1" displayName="Table1" ref="B6:D7" totalsRowShown="0" headerRowDxfId="12" headerRowBorderDxfId="11" tableBorderDxfId="10" totalsRowBorderDxfId="9">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{60F36206-4025-444C-97F9-5648758DD05C}" name="unique_product_2020" dataDxfId="32"/>
-    <tableColumn id="2" xr3:uid="{1BC7FA7B-C996-4BE3-B0F0-5700AED7CCD3}" name="unique_products_2021" dataDxfId="31"/>
-    <tableColumn id="3" xr3:uid="{E7FE8A4B-C989-4996-8231-D127C40B70DE}" name="percentage_chg" dataDxfId="30"/>
+    <tableColumn id="1" xr3:uid="{60F36206-4025-444C-97F9-5648758DD05C}" name="unique_product_2020" dataDxfId="8"/>
+    <tableColumn id="2" xr3:uid="{1BC7FA7B-C996-4BE3-B0F0-5700AED7CCD3}" name="unique_products_2021" dataDxfId="7"/>
+    <tableColumn id="3" xr3:uid="{E7FE8A4B-C989-4996-8231-D127C40B70DE}" name="percentage_chg" dataDxfId="6"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10142,18 +9766,18 @@
   <tableColumns count="3">
     <tableColumn id="1" xr3:uid="{C9EAF05D-FC23-4483-B500-1A3AA5459A84}" name="product_code"/>
     <tableColumn id="2" xr3:uid="{EEFF9F2E-BDE2-40CA-BE40-6572BBB69BF2}" name="product"/>
-    <tableColumn id="3" xr3:uid="{B7D30907-70A0-4D3A-B56C-39352F7AB802}" name="manufacturing_cost" dataDxfId="29"/>
+    <tableColumn id="3" xr3:uid="{B7D30907-70A0-4D3A-B56C-39352F7AB802}" name="manufacturing_cost" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D248CE95-FCFA-4449-8DBB-0817001DE4BF}" name="Table15" displayName="Table15" ref="B5:D10" totalsRowShown="0" headerRowDxfId="12" dataDxfId="28">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{D248CE95-FCFA-4449-8DBB-0817001DE4BF}" name="Table15" displayName="Table15" ref="B5:D10" totalsRowShown="0" headerRowDxfId="4" dataDxfId="3">
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{0CF72AB0-D99B-4299-B396-20E0BFE965CD}" name="customer_code" dataDxfId="27"/>
-    <tableColumn id="2" xr3:uid="{2BDA3698-9A09-4CFC-A180-51CD3DBBB4A3}" name="customer" dataDxfId="26"/>
-    <tableColumn id="3" xr3:uid="{A38C5E30-5715-4510-8DAE-ED30282AA105}" name="average_discount_percentage" dataDxfId="25" dataCellStyle="Percent"/>
+    <tableColumn id="1" xr3:uid="{0CF72AB0-D99B-4299-B396-20E0BFE965CD}" name="customer_code" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{2BDA3698-9A09-4CFC-A180-51CD3DBBB4A3}" name="customer" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{A38C5E30-5715-4510-8DAE-ED30282AA105}" name="average_discount_percentage" dataDxfId="0" dataCellStyle="Percent"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -10475,45 +10099,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>95</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -10585,48 +10209,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -10778,45 +10402,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="19" t="s">
         <v>72</v>
       </c>
-      <c r="B1" s="19"/>
-      <c r="C1" s="19"/>
-      <c r="D1" s="19"/>
-      <c r="E1" s="19"/>
-      <c r="F1" s="19"/>
-      <c r="G1" s="19"/>
-      <c r="H1" s="19"/>
-      <c r="I1" s="19"/>
-      <c r="J1" s="19"/>
-      <c r="K1" s="19"/>
+      <c r="B1" s="20"/>
+      <c r="C1" s="20"/>
+      <c r="D1" s="20"/>
+      <c r="E1" s="20"/>
+      <c r="F1" s="20"/>
+      <c r="G1" s="20"/>
+      <c r="H1" s="20"/>
+      <c r="I1" s="20"/>
+      <c r="J1" s="20"/>
+      <c r="K1" s="20"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="19"/>
-      <c r="B2" s="19"/>
-      <c r="C2" s="19"/>
-      <c r="D2" s="19"/>
-      <c r="E2" s="19"/>
-      <c r="F2" s="19"/>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
+      <c r="A2" s="20"/>
+      <c r="B2" s="20"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="19"/>
-      <c r="B3" s="19"/>
-      <c r="C3" s="19"/>
-      <c r="D3" s="19"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
+      <c r="A3" s="20"/>
+      <c r="B3" s="20"/>
+      <c r="C3" s="20"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="20"/>
+      <c r="F3" s="20"/>
+      <c r="G3" s="20"/>
+      <c r="H3" s="20"/>
+      <c r="I3" s="20"/>
+      <c r="J3" s="20"/>
+      <c r="K3" s="20"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
@@ -10862,45 +10486,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>96</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
@@ -10981,45 +10605,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>73</v>
       </c>
-      <c r="B1" s="17"/>
-      <c r="C1" s="17"/>
-      <c r="D1" s="17"/>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="17"/>
-      <c r="H1" s="17"/>
-      <c r="I1" s="17"/>
-      <c r="J1" s="17"/>
-      <c r="K1" s="17"/>
+      <c r="B1" s="18"/>
+      <c r="C1" s="18"/>
+      <c r="D1" s="18"/>
+      <c r="E1" s="18"/>
+      <c r="F1" s="18"/>
+      <c r="G1" s="18"/>
+      <c r="H1" s="18"/>
+      <c r="I1" s="18"/>
+      <c r="J1" s="18"/>
+      <c r="K1" s="18"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
-      <c r="D2" s="17"/>
-      <c r="E2" s="17"/>
-      <c r="F2" s="17"/>
-      <c r="G2" s="17"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
-      <c r="J2" s="17"/>
-      <c r="K2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
+      <c r="C2" s="18"/>
+      <c r="D2" s="18"/>
+      <c r="E2" s="18"/>
+      <c r="F2" s="18"/>
+      <c r="G2" s="18"/>
+      <c r="H2" s="18"/>
+      <c r="I2" s="18"/>
+      <c r="J2" s="18"/>
+      <c r="K2" s="18"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="17"/>
-      <c r="B3" s="17"/>
-      <c r="C3" s="17"/>
-      <c r="D3" s="17"/>
-      <c r="E3" s="17"/>
-      <c r="F3" s="17"/>
-      <c r="G3" s="17"/>
-      <c r="H3" s="17"/>
-      <c r="I3" s="17"/>
-      <c r="J3" s="17"/>
-      <c r="K3" s="17"/>
+      <c r="A3" s="18"/>
+      <c r="B3" s="18"/>
+      <c r="C3" s="18"/>
+      <c r="D3" s="18"/>
+      <c r="E3" s="18"/>
+      <c r="F3" s="18"/>
+      <c r="G3" s="18"/>
+      <c r="H3" s="18"/>
+      <c r="I3" s="18"/>
+      <c r="J3" s="18"/>
+      <c r="K3" s="18"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
@@ -11143,45 +10767,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>74</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B5" t="s">
@@ -11240,54 +10864,54 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>75</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" ht="40.799999999999997" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C5" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="D5" s="23" t="s">
+      <c r="D5" s="15" t="s">
         <v>60</v>
       </c>
     </row>
@@ -11368,48 +10992,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="16" t="s">
         <v>79</v>
       </c>
-      <c r="B1" s="16"/>
-      <c r="C1" s="16"/>
-      <c r="D1" s="16"/>
-      <c r="E1" s="16"/>
-      <c r="F1" s="16"/>
-      <c r="G1" s="16"/>
-      <c r="H1" s="16"/>
-      <c r="I1" s="16"/>
-      <c r="J1" s="16"/>
-      <c r="K1" s="16"/>
-      <c r="L1" s="16"/>
+      <c r="B1" s="17"/>
+      <c r="C1" s="17"/>
+      <c r="D1" s="17"/>
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="17"/>
+      <c r="H1" s="17"/>
+      <c r="I1" s="17"/>
+      <c r="J1" s="17"/>
+      <c r="K1" s="17"/>
+      <c r="L1" s="17"/>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A2" s="16"/>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-      <c r="I2" s="16"/>
-      <c r="J2" s="16"/>
-      <c r="K2" s="16"/>
-      <c r="L2" s="16"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
+      <c r="J2" s="17"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-      <c r="I3" s="16"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+      <c r="I3" s="17"/>
+      <c r="J3" s="17"/>
+      <c r="K3" s="17"/>
+      <c r="L3" s="17"/>
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
@@ -11424,13 +11048,13 @@
     </row>
     <row r="6" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A6">
-        <v>2018</v>
+        <v>2021</v>
       </c>
       <c r="B6" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C6" s="12">
-        <v>2347703.88</v>
+        <v>37752848.189999998</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11438,7 +11062,7 @@
         <v>84</v>
       </c>
       <c r="C7" s="12">
-        <v>2462780.5499999998</v>
+        <v>40444450.560000002</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11446,7 +11070,7 @@
         <v>85</v>
       </c>
       <c r="C8" s="12">
-        <v>3766114.43</v>
+        <v>62302295.57</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11454,7 +11078,7 @@
         <v>86</v>
       </c>
       <c r="C9" s="12">
-        <v>2390015.56</v>
+        <v>39306619.909999996</v>
       </c>
     </row>
     <row r="10" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11462,7 +11086,7 @@
         <v>87</v>
       </c>
       <c r="C10" s="12">
-        <v>2285937.67</v>
+        <v>37704996.299999997</v>
       </c>
     </row>
     <row r="11" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11470,7 +11094,7 @@
         <v>88</v>
       </c>
       <c r="C11" s="12">
-        <v>1985466.36</v>
+        <v>30852326.32</v>
       </c>
     </row>
     <row r="12" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11478,7 +11102,7 @@
         <v>89</v>
       </c>
       <c r="C12" s="12">
-        <v>2219880.14</v>
+        <v>36972600.020000003</v>
       </c>
     </row>
     <row r="13" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11486,7 +11110,7 @@
         <v>90</v>
       </c>
       <c r="C13" s="12">
-        <v>1392024.51</v>
+        <v>22147394.989999998</v>
       </c>
     </row>
     <row r="14" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11494,7 +11118,7 @@
         <v>91</v>
       </c>
       <c r="C14" s="12">
-        <v>2310946.52</v>
+        <v>37037201.240000002</v>
       </c>
     </row>
     <row r="15" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11502,7 +11126,7 @@
         <v>92</v>
       </c>
       <c r="C15" s="12">
-        <v>1976109.61</v>
+        <v>29887193.879999999</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.6" x14ac:dyDescent="0.3">
@@ -11510,7 +11134,7 @@
         <v>93</v>
       </c>
       <c r="C16" s="12">
-        <v>2224693.7599999998</v>
+        <v>36677913.909999996</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -11518,18 +11142,18 @@
         <v>94</v>
       </c>
       <c r="C17" s="12">
-        <v>1498728.56</v>
+        <v>21839400.719999999</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
       <c r="A18">
-        <v>2019</v>
+        <v>2022</v>
       </c>
       <c r="B18" s="13" t="s">
         <v>83</v>
       </c>
       <c r="C18" s="12">
-        <v>7860039.25</v>
+        <v>153599487.94999999</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -11537,7 +11161,7 @@
         <v>84</v>
       </c>
       <c r="C19" s="12">
-        <v>8496754.2300000004</v>
+        <v>159240254.33000001</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -11545,7 +11169,7 @@
         <v>85</v>
       </c>
       <c r="C20" s="12">
-        <v>12362495.369999999</v>
+        <v>259105977.18000001</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
@@ -11553,306 +11177,45 @@
         <v>86</v>
       </c>
       <c r="C21" s="12">
-        <v>8364101.0199999996</v>
+        <v>161727839.58000001</v>
       </c>
     </row>
-    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B22" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C22" s="12">
-        <v>7607522.3600000003</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B23" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C23" s="12">
-        <v>6218859.5700000003</v>
-      </c>
-    </row>
-    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B24" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C24" s="12">
-        <v>7307169.1500000004</v>
-      </c>
-    </row>
-    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B25" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C25" s="12">
-        <v>4677628.0999999996</v>
-      </c>
-    </row>
-    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B26" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C26" s="12">
-        <v>7796837.2999999998</v>
-      </c>
-    </row>
-    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B27" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C27" s="12">
-        <v>6580393.9800000004</v>
-      </c>
-    </row>
-    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B28" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C28" s="12">
-        <v>7296958.9800000004</v>
-      </c>
-    </row>
-    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B29" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C29" s="12">
-        <v>4630439.42</v>
-      </c>
-    </row>
-    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A30">
-        <v>2020</v>
-      </c>
-      <c r="B30" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C30" s="12">
-        <v>17040562.239999998</v>
-      </c>
-    </row>
-    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B31" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C31" s="12">
-        <v>19475069.34</v>
-      </c>
-    </row>
-    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B32" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C32" s="12">
-        <v>28512004.149999999</v>
-      </c>
-    </row>
-    <row r="33" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B33" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C33" s="12">
-        <v>18322529.100000001</v>
-      </c>
-    </row>
-    <row r="34" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B34" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C34" s="12">
-        <v>18009123.489999998</v>
-      </c>
-    </row>
-    <row r="35" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B35" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C35" s="12">
-        <v>15171931.84</v>
-      </c>
-    </row>
-    <row r="36" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B36" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C36" s="12">
-        <v>1422525.16</v>
-      </c>
-    </row>
-    <row r="37" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B37" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C37" s="12">
-        <v>1492369.18</v>
-      </c>
-    </row>
-    <row r="38" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B38" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C38" s="12">
-        <v>2971173.85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B39" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C39" s="12">
-        <v>6451963.4100000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B40" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C40" s="12">
-        <v>9685828.6300000008</v>
-      </c>
-    </row>
-    <row r="41" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B41" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C41" s="12">
-        <v>10599401.49</v>
-      </c>
-    </row>
-    <row r="42" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A42">
-        <v>2021</v>
-      </c>
-      <c r="B42" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C42" s="12">
-        <v>37752848.189999998</v>
-      </c>
-    </row>
-    <row r="43" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B43" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C43" s="12">
-        <v>40444450.560000002</v>
-      </c>
-    </row>
-    <row r="44" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B44" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C44" s="12">
-        <v>62302295.57</v>
-      </c>
-    </row>
-    <row r="45" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B45" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C45" s="12">
-        <v>39306619.909999996</v>
-      </c>
-    </row>
-    <row r="46" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B46" s="13" t="s">
-        <v>87</v>
-      </c>
-      <c r="C46" s="12">
-        <v>37704996.299999997</v>
-      </c>
-    </row>
-    <row r="47" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B47" s="13" t="s">
-        <v>88</v>
-      </c>
-      <c r="C47" s="12">
-        <v>30852326.32</v>
-      </c>
-    </row>
-    <row r="48" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B48" s="13" t="s">
-        <v>89</v>
-      </c>
-      <c r="C48" s="12">
-        <v>36972600.020000003</v>
-      </c>
-    </row>
-    <row r="49" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B49" s="13" t="s">
-        <v>90</v>
-      </c>
-      <c r="C49" s="12">
-        <v>22147394.989999998</v>
-      </c>
-    </row>
-    <row r="50" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B50" s="13" t="s">
-        <v>91</v>
-      </c>
-      <c r="C50" s="12">
-        <v>37037201.240000002</v>
-      </c>
-    </row>
-    <row r="51" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B51" s="13" t="s">
-        <v>92</v>
-      </c>
-      <c r="C51" s="12">
-        <v>29887193.879999999</v>
-      </c>
-    </row>
-    <row r="52" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B52" s="13" t="s">
-        <v>93</v>
-      </c>
-      <c r="C52" s="12">
-        <v>36677913.909999996</v>
-      </c>
-    </row>
-    <row r="53" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B53" s="13" t="s">
-        <v>94</v>
-      </c>
-      <c r="C53" s="12">
-        <v>21839400.719999999</v>
-      </c>
-    </row>
-    <row r="54" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="A54">
-        <v>2022</v>
-      </c>
-      <c r="B54" s="13" t="s">
-        <v>83</v>
-      </c>
-      <c r="C54" s="12">
-        <v>153599487.94999999</v>
-      </c>
-    </row>
-    <row r="55" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B55" s="13" t="s">
-        <v>84</v>
-      </c>
-      <c r="C55" s="12">
-        <v>159240254.33000001</v>
-      </c>
-    </row>
-    <row r="56" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B56" s="13" t="s">
-        <v>85</v>
-      </c>
-      <c r="C56" s="12">
-        <v>259105977.18000001</v>
-      </c>
-    </row>
-    <row r="57" spans="1:3" ht="15.6" x14ac:dyDescent="0.3">
-      <c r="B57" s="13" t="s">
-        <v>86</v>
-      </c>
-      <c r="C57" s="12">
-        <v>161727839.58000001</v>
-      </c>
-    </row>
+    <row r="22" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="23" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="24" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="25" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="26" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="27" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="28" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="29" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="30" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="31" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="32" spans="1:3" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="33" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="34" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="35" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="36" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="37" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="38" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="39" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="40" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="41" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="42" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="43" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="44" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="45" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="46" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="47" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="48" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="49" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="50" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="51" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="52" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="53" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="54" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="55" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="56" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="57" ht="15.6" x14ac:dyDescent="0.3"/>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A1:L3"/>
@@ -11873,45 +11236,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="23" t="s">
         <v>76</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
@@ -11976,45 +11339,45 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A1" s="20" t="s">
+      <c r="A1" s="21" t="s">
         <v>77</v>
       </c>
-      <c r="B1" s="21"/>
-      <c r="C1" s="21"/>
-      <c r="D1" s="21"/>
-      <c r="E1" s="21"/>
-      <c r="F1" s="21"/>
-      <c r="G1" s="21"/>
-      <c r="H1" s="21"/>
-      <c r="I1" s="21"/>
-      <c r="J1" s="21"/>
-      <c r="K1" s="21"/>
+      <c r="B1" s="22"/>
+      <c r="C1" s="22"/>
+      <c r="D1" s="22"/>
+      <c r="E1" s="22"/>
+      <c r="F1" s="22"/>
+      <c r="G1" s="22"/>
+      <c r="H1" s="22"/>
+      <c r="I1" s="22"/>
+      <c r="J1" s="22"/>
+      <c r="K1" s="22"/>
     </row>
     <row r="2" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A2" s="21"/>
-      <c r="B2" s="21"/>
-      <c r="C2" s="21"/>
-      <c r="D2" s="21"/>
-      <c r="E2" s="21"/>
-      <c r="F2" s="21"/>
-      <c r="G2" s="21"/>
-      <c r="H2" s="21"/>
-      <c r="I2" s="21"/>
-      <c r="J2" s="21"/>
-      <c r="K2" s="21"/>
+      <c r="A2" s="22"/>
+      <c r="B2" s="22"/>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
+      <c r="F2" s="22"/>
+      <c r="G2" s="22"/>
+      <c r="H2" s="22"/>
+      <c r="I2" s="22"/>
+      <c r="J2" s="22"/>
+      <c r="K2" s="22"/>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A3" s="21"/>
-      <c r="B3" s="21"/>
-      <c r="C3" s="21"/>
-      <c r="D3" s="21"/>
-      <c r="E3" s="21"/>
-      <c r="F3" s="21"/>
-      <c r="G3" s="21"/>
-      <c r="H3" s="21"/>
-      <c r="I3" s="21"/>
-      <c r="J3" s="21"/>
-      <c r="K3" s="21"/>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="22"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
